--- a/src/results/cr/regresiones_dependientes/wages.xlsx
+++ b/src/results/cr/regresiones_dependientes/wages.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,175 +500,250 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P Comp +15</t>
+          <t>P Inc -15</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1810</v>
+        <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>248</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>217</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>249</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>331</v>
+        <v>6</v>
       </c>
       <c r="G2" t="n">
-        <v>219</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S Inc -15</t>
+          <t>P Inc +15</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>796</v>
+        <v>308</v>
       </c>
       <c r="C3" t="n">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="D3" t="n">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="E3" t="n">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="F3" t="n">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="G3" t="n">
-        <v>91</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S Inc+15</t>
+          <t>P Comp -15</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1390</v>
+        <v>200</v>
       </c>
       <c r="C4" t="n">
-        <v>190</v>
+        <v>18</v>
       </c>
       <c r="D4" t="n">
-        <v>158</v>
+        <v>23</v>
       </c>
       <c r="E4" t="n">
-        <v>134</v>
+        <v>11</v>
       </c>
       <c r="F4" t="n">
-        <v>160</v>
+        <v>36</v>
       </c>
       <c r="G4" t="n">
-        <v>128</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S Comp -15</t>
+          <t>P Comp +15</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2061</v>
+        <v>1610</v>
       </c>
       <c r="C5" t="n">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="D5" t="n">
-        <v>151</v>
+        <v>194</v>
       </c>
       <c r="E5" t="n">
-        <v>218</v>
+        <v>238</v>
       </c>
       <c r="F5" t="n">
-        <v>259</v>
+        <v>295</v>
       </c>
       <c r="G5" t="n">
-        <v>167</v>
+        <v>199</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S Comp +15</t>
+          <t>S Inc -15</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1387</v>
+        <v>796</v>
       </c>
       <c r="C6" t="n">
-        <v>250</v>
+        <v>96</v>
       </c>
       <c r="D6" t="n">
-        <v>152</v>
+        <v>78</v>
       </c>
       <c r="E6" t="n">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="F6" t="n">
-        <v>172</v>
+        <v>109</v>
       </c>
       <c r="G6" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ter -15</t>
+          <t>S Inc+15</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4283</v>
+        <v>1390</v>
       </c>
       <c r="C7" t="n">
-        <v>424</v>
+        <v>190</v>
       </c>
       <c r="D7" t="n">
-        <v>241</v>
+        <v>158</v>
       </c>
       <c r="E7" t="n">
-        <v>377</v>
+        <v>134</v>
       </c>
       <c r="F7" t="n">
-        <v>339</v>
+        <v>160</v>
       </c>
       <c r="G7" t="n">
-        <v>237</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>S Comp -15</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2061</v>
+      </c>
+      <c r="C8" t="n">
+        <v>215</v>
+      </c>
+      <c r="D8" t="n">
+        <v>151</v>
+      </c>
+      <c r="E8" t="n">
+        <v>218</v>
+      </c>
+      <c r="F8" t="n">
+        <v>259</v>
+      </c>
+      <c r="G8" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>S Comp +15</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1387</v>
+      </c>
+      <c r="C9" t="n">
+        <v>250</v>
+      </c>
+      <c r="D9" t="n">
+        <v>152</v>
+      </c>
+      <c r="E9" t="n">
+        <v>117</v>
+      </c>
+      <c r="F9" t="n">
+        <v>172</v>
+      </c>
+      <c r="G9" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Ter -15</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>4283</v>
+      </c>
+      <c r="C10" t="n">
+        <v>424</v>
+      </c>
+      <c r="D10" t="n">
+        <v>241</v>
+      </c>
+      <c r="E10" t="n">
+        <v>377</v>
+      </c>
+      <c r="F10" t="n">
+        <v>339</v>
+      </c>
+      <c r="G10" t="n">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Ter +15</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B11" t="n">
         <v>3512</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C11" t="n">
         <v>422</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D11" t="n">
         <v>226</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E11" t="n">
         <v>325</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F11" t="n">
         <v>260</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G11" t="n">
         <v>179</v>
       </c>
     </row>
@@ -683,7 +758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -731,1477 +806,2002 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P Comp +15</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>310</v>
-      </c>
-      <c r="C3" t="n">
-        <v>39</v>
-      </c>
-      <c r="D3" t="n">
-        <v>39</v>
-      </c>
-      <c r="E3" t="n">
-        <v>40</v>
-      </c>
-      <c r="F3" t="n">
-        <v>68</v>
-      </c>
-      <c r="G3" t="n">
-        <v>37</v>
+          <t>P Inc -15</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S Inc -15</t>
+          <t>P Inc +15</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>11</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F4" t="n">
         <v>23</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S Inc+15</t>
+          <t>P Comp -15</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>244</v>
-      </c>
-      <c r="C5" t="n">
-        <v>33</v>
-      </c>
-      <c r="D5" t="n">
-        <v>22</v>
+        <v>35</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="F5" t="n">
-        <v>25</v>
+        <v>2</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>11</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S Comp -15</t>
+          <t>P Comp +15</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>297</v>
+        <v>275</v>
       </c>
       <c r="C6" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="D6" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="E6" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F6" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="G6" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S Comp +15</t>
+          <t>S Inc -15</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>195</v>
-      </c>
-      <c r="C7" t="n">
-        <v>28</v>
+        <v>150</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>17</v>
       </c>
       <c r="D7" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="E7" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="E7" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>18</v>
+      <c r="F7" t="n">
+        <v>23</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ter -15</t>
+          <t>S Inc+15</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>701</v>
+        <v>244</v>
       </c>
       <c r="C8" t="n">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="D8" t="n">
-        <v>34</v>
-      </c>
-      <c r="E8" t="n">
-        <v>56</v>
+        <v>22</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>20</v>
       </c>
       <c r="F8" t="n">
-        <v>56</v>
-      </c>
-      <c r="G8" t="n">
-        <v>37</v>
+        <v>25</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ter +15</t>
+          <t>S Comp -15</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>440</v>
+        <v>297</v>
       </c>
       <c r="C9" t="n">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="D9" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F9" t="n">
         <v>40</v>
       </c>
       <c r="G9" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>S Comp +15</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>195</v>
+      </c>
+      <c r="C10" t="n">
+        <v>28</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Ter -15</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>701</v>
+      </c>
+      <c r="C11" t="n">
+        <v>61</v>
+      </c>
+      <c r="D11" t="n">
+        <v>34</v>
+      </c>
+      <c r="E11" t="n">
+        <v>56</v>
+      </c>
+      <c r="F11" t="n">
+        <v>56</v>
+      </c>
+      <c r="G11" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ter +15</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>440</v>
+      </c>
+      <c r="C12" t="n">
+        <v>64</v>
+      </c>
+      <c r="D12" t="n">
+        <v>31</v>
+      </c>
+      <c r="E12" t="n">
+        <v>42</v>
+      </c>
+      <c r="F12" t="n">
+        <v>40</v>
+      </c>
+      <c r="G12" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
+    <row r="14">
+      <c r="A14" t="n">
         <v>2016</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>habilidad</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Central</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Chorotega</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Pacífico Central</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Brunca</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Huetar Caribe</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>Huetar Norte</t>
         </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>P Comp +15</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>361</v>
-      </c>
-      <c r="C13" t="n">
-        <v>47</v>
-      </c>
-      <c r="D13" t="n">
-        <v>36</v>
-      </c>
-      <c r="E13" t="n">
-        <v>50</v>
-      </c>
-      <c r="F13" t="n">
-        <v>62</v>
-      </c>
-      <c r="G13" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>S Inc -15</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>140</v>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>S Inc+15</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>201</v>
-      </c>
-      <c r="C15" t="n">
-        <v>21</v>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S Comp -15</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>323</v>
-      </c>
-      <c r="C16" t="n">
-        <v>28</v>
+          <t>P Inc -15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="E16" t="n">
-        <v>31</v>
-      </c>
-      <c r="F16" t="n">
-        <v>23</v>
-      </c>
-      <c r="G16" t="n">
-        <v>31</v>
+        <v>0</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S Comp +15</t>
+          <t>P Inc +15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>203</v>
-      </c>
-      <c r="C17" t="n">
-        <v>38</v>
+        <v>55</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>15</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="F17" t="n">
-        <v>22</v>
+        <v>18</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>20</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ter -15</t>
+          <t>P Comp -15</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>670</v>
-      </c>
-      <c r="C18" t="n">
-        <v>68</v>
-      </c>
-      <c r="D18" t="n">
-        <v>35</v>
-      </c>
-      <c r="E18" t="n">
-        <v>61</v>
-      </c>
-      <c r="F18" t="n">
-        <v>50</v>
-      </c>
-      <c r="G18" t="n">
-        <v>33</v>
+        <v>52</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ter +15</t>
+          <t>P Comp +15</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>465</v>
+        <v>309</v>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="D19" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E19" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="F19" t="n">
-        <v>27</v>
-      </c>
-      <c r="G19" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="G19" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>S Inc -15</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>140</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>17</v>
       </c>
+      <c r="D20" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>2017</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>S Inc+15</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>201</v>
+      </c>
+      <c r="C21" t="n">
+        <v>21</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>habilidad</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Central</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Chorotega</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Pacífico Central</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Brunca</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Huetar Caribe</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>Huetar Norte</t>
-        </is>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>S Comp -15</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>323</v>
+      </c>
+      <c r="C22" t="n">
+        <v>28</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="E22" t="n">
+        <v>31</v>
+      </c>
+      <c r="F22" t="n">
+        <v>23</v>
+      </c>
+      <c r="G22" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P Comp +15</t>
+          <t>S Comp +15</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>286</v>
+        <v>203</v>
       </c>
       <c r="C23" t="n">
-        <v>31</v>
-      </c>
-      <c r="D23" t="n">
-        <v>33</v>
-      </c>
-      <c r="E23" t="n">
-        <v>47</v>
+        <v>38</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>15</v>
       </c>
       <c r="F23" t="n">
-        <v>48</v>
-      </c>
-      <c r="G23" t="n">
-        <v>29</v>
+        <v>22</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S Inc -15</t>
+          <t>Ter -15</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>143</v>
-      </c>
-      <c r="C24" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="D24" s="3" t="n">
-        <v>18</v>
+        <v>670</v>
+      </c>
+      <c r="C24" t="n">
+        <v>68</v>
+      </c>
+      <c r="D24" t="n">
+        <v>35</v>
       </c>
       <c r="E24" t="n">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="F24" t="n">
-        <v>24</v>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>15</v>
+        <v>50</v>
+      </c>
+      <c r="G24" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S Inc+15</t>
+          <t>Ter +15</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>199</v>
+        <v>465</v>
       </c>
       <c r="C25" t="n">
-        <v>26</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>20</v>
+        <v>56</v>
+      </c>
+      <c r="D25" t="n">
+        <v>37</v>
+      </c>
+      <c r="E25" t="n">
+        <v>41</v>
       </c>
       <c r="F25" t="n">
         <v>27</v>
       </c>
-      <c r="G25" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>S Comp -15</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>287</v>
-      </c>
-      <c r="C26" t="n">
-        <v>33</v>
-      </c>
-      <c r="D26" t="n">
-        <v>21</v>
-      </c>
-      <c r="E26" t="n">
-        <v>25</v>
-      </c>
-      <c r="F26" t="n">
-        <v>28</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>20</v>
+      <c r="G25" s="3" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>S Comp +15</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>180</v>
-      </c>
-      <c r="C27" t="n">
-        <v>35</v>
-      </c>
-      <c r="D27" t="n">
-        <v>28</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="F27" t="n">
-        <v>22</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>10</v>
+      <c r="A27" t="n">
+        <v>2017</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Ter -15</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>601</v>
-      </c>
-      <c r="C28" t="n">
-        <v>57</v>
-      </c>
-      <c r="D28" t="n">
-        <v>38</v>
-      </c>
-      <c r="E28" t="n">
-        <v>55</v>
-      </c>
-      <c r="F28" t="n">
-        <v>50</v>
-      </c>
-      <c r="G28" t="n">
-        <v>30</v>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>habilidad</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Chorotega</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Pacífico Central</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Brunca</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Huetar Caribe</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Huetar Norte</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Ter +15</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>471</v>
-      </c>
-      <c r="C29" t="n">
-        <v>61</v>
-      </c>
-      <c r="D29" t="n">
-        <v>31</v>
-      </c>
-      <c r="E29" t="n">
-        <v>40</v>
-      </c>
-      <c r="F29" t="n">
+          <t>P Inc -15</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>P Inc +15</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>51</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F30" t="n">
+        <v>23</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>P Comp -15</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>36</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>P Comp +15</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>250</v>
+      </c>
+      <c r="C32" t="n">
         <v>29</v>
       </c>
-      <c r="G29" s="3" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>2018</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>habilidad</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Central</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Chorotega</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Pacífico Central</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Brunca</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>Huetar Caribe</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Huetar Norte</t>
-        </is>
+      <c r="D32" t="n">
+        <v>28</v>
+      </c>
+      <c r="E32" t="n">
+        <v>44</v>
+      </c>
+      <c r="F32" t="n">
+        <v>45</v>
+      </c>
+      <c r="G32" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>P Comp +15</t>
+          <t>S Inc -15</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>246</v>
-      </c>
-      <c r="C33" t="n">
-        <v>37</v>
-      </c>
-      <c r="D33" t="n">
-        <v>25</v>
+        <v>143</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>18</v>
       </c>
       <c r="E33" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="F33" t="n">
-        <v>51</v>
-      </c>
-      <c r="G33" t="n">
-        <v>32</v>
+        <v>24</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S Inc -15</t>
+          <t>S Inc+15</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>119</v>
-      </c>
-      <c r="C34" s="3" t="n">
-        <v>18</v>
+        <v>199</v>
+      </c>
+      <c r="C34" t="n">
+        <v>26</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="E34" t="n">
+        <v>19</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F34" t="n">
+        <v>27</v>
+      </c>
+      <c r="G34" t="n">
         <v>21</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="G34" s="3" t="n">
-        <v>17</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S Inc+15</t>
+          <t>S Comp -15</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>210</v>
+        <v>287</v>
       </c>
       <c r="C35" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D35" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E35" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F35" t="n">
-        <v>23</v>
-      </c>
-      <c r="G35" t="n">
-        <v>22</v>
+        <v>28</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S Comp -15</t>
+          <t>S Comp +15</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>294</v>
+        <v>180</v>
       </c>
       <c r="C36" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D36" t="n">
-        <v>23</v>
-      </c>
-      <c r="E36" t="n">
-        <v>34</v>
+        <v>28</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>17</v>
       </c>
       <c r="F36" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S Comp +15</t>
+          <t>Ter -15</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>175</v>
+        <v>601</v>
       </c>
       <c r="C37" t="n">
-        <v>35</v>
-      </c>
-      <c r="D37" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>15</v>
+        <v>57</v>
+      </c>
+      <c r="D37" t="n">
+        <v>38</v>
+      </c>
+      <c r="E37" t="n">
+        <v>55</v>
       </c>
       <c r="F37" t="n">
-        <v>25</v>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>17</v>
+        <v>50</v>
+      </c>
+      <c r="G37" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Ter -15</t>
+          <t>Ter +15</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>615</v>
+        <v>471</v>
       </c>
       <c r="C38" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D38" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E38" t="n">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="F38" t="n">
-        <v>47</v>
-      </c>
-      <c r="G38" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Ter +15</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>516</v>
-      </c>
-      <c r="C39" t="n">
-        <v>58</v>
-      </c>
-      <c r="D39" t="n">
-        <v>31</v>
-      </c>
-      <c r="E39" t="n">
-        <v>44</v>
-      </c>
-      <c r="F39" t="n">
-        <v>33</v>
-      </c>
-      <c r="G39" t="n">
-        <v>23</v>
+        <v>29</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2018</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="n">
-        <v>2019</v>
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>habilidad</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Chorotega</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Pacífico Central</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Brunca</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Huetar Caribe</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Huetar Norte</t>
+        </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>habilidad</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Central</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Chorotega</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Pacífico Central</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>Brunca</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>Huetar Caribe</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>Huetar Norte</t>
-        </is>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>P Inc -15</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>P Comp +15</t>
+          <t>P Inc +15</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>243</v>
-      </c>
-      <c r="C43" t="n">
-        <v>45</v>
-      </c>
-      <c r="D43" t="n">
-        <v>33</v>
-      </c>
-      <c r="E43" t="n">
-        <v>36</v>
-      </c>
-      <c r="F43" t="n">
-        <v>46</v>
-      </c>
-      <c r="G43" t="n">
-        <v>31</v>
+        <v>51</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S Inc -15</t>
+          <t>P Comp -15</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S Inc+15</t>
+          <t>P Comp +15</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="C45" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D45" t="n">
+        <v>23</v>
+      </c>
+      <c r="E45" t="n">
+        <v>33</v>
+      </c>
+      <c r="F45" t="n">
+        <v>46</v>
+      </c>
+      <c r="G45" t="n">
         <v>30</v>
-      </c>
-      <c r="E45" t="n">
-        <v>23</v>
-      </c>
-      <c r="F45" t="n">
-        <v>33</v>
-      </c>
-      <c r="G45" t="n">
-        <v>26</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S Comp -15</t>
+          <t>S Inc -15</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>272</v>
-      </c>
-      <c r="C46" t="n">
-        <v>36</v>
+        <v>119</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>18</v>
       </c>
       <c r="D46" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="E46" t="n">
+        <v>21</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="G46" s="3" t="n">
         <v>17</v>
-      </c>
-      <c r="E46" t="n">
-        <v>37</v>
-      </c>
-      <c r="F46" t="n">
-        <v>36</v>
-      </c>
-      <c r="G46" t="n">
-        <v>25</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S Comp +15</t>
+          <t>S Inc+15</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C47" t="n">
-        <v>29</v>
-      </c>
-      <c r="D47" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="E47" s="3" t="n">
-        <v>17</v>
+        <v>26</v>
+      </c>
+      <c r="D47" t="n">
+        <v>30</v>
+      </c>
+      <c r="E47" t="n">
+        <v>23</v>
       </c>
       <c r="F47" t="n">
-        <v>30</v>
-      </c>
-      <c r="G47" s="3" t="n">
-        <v>9</v>
+        <v>23</v>
+      </c>
+      <c r="G47" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Ter -15</t>
+          <t>S Comp -15</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>624</v>
+        <v>294</v>
       </c>
       <c r="C48" t="n">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="D48" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="E48" t="n">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="F48" t="n">
-        <v>40</v>
-      </c>
-      <c r="G48" t="n">
-        <v>33</v>
+        <v>35</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>S Comp +15</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>175</v>
+      </c>
+      <c r="C49" t="n">
+        <v>35</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F49" t="n">
+        <v>25</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Ter -15</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>615</v>
+      </c>
+      <c r="C50" t="n">
+        <v>58</v>
+      </c>
+      <c r="D50" t="n">
+        <v>38</v>
+      </c>
+      <c r="E50" t="n">
+        <v>62</v>
+      </c>
+      <c r="F50" t="n">
+        <v>47</v>
+      </c>
+      <c r="G50" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>Ter +15</t>
         </is>
       </c>
-      <c r="B49" t="n">
-        <v>518</v>
-      </c>
-      <c r="C49" t="n">
-        <v>57</v>
-      </c>
-      <c r="D49" t="n">
-        <v>27</v>
-      </c>
-      <c r="E49" t="n">
-        <v>49</v>
-      </c>
-      <c r="F49" t="n">
-        <v>34</v>
-      </c>
-      <c r="G49" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="B51" t="n">
+        <v>516</v>
+      </c>
+      <c r="C51" t="n">
+        <v>58</v>
+      </c>
+      <c r="D51" t="n">
+        <v>31</v>
+      </c>
+      <c r="E51" t="n">
+        <v>44</v>
+      </c>
+      <c r="F51" t="n">
+        <v>33</v>
+      </c>
+      <c r="G51" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>habilidad</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>Central</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>Chorotega</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Pacífico Central</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Brunca</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Huetar Caribe</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>Huetar Norte</t>
         </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>P Comp +15</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>167</v>
-      </c>
-      <c r="C53" t="n">
-        <v>25</v>
-      </c>
-      <c r="D53" t="n">
-        <v>23</v>
-      </c>
-      <c r="E53" t="n">
-        <v>23</v>
-      </c>
-      <c r="F53" t="n">
-        <v>29</v>
-      </c>
-      <c r="G53" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>S Inc -15</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>63</v>
-      </c>
-      <c r="C54" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="D54" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="E54" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F54" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="G54" s="3" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S Inc+15</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>170</v>
-      </c>
-      <c r="C55" t="n">
-        <v>27</v>
+          <t>P Inc -15</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>S Comp -15</t>
+          <t>P Inc +15</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>277</v>
-      </c>
-      <c r="C56" t="n">
-        <v>37</v>
-      </c>
-      <c r="D56" t="n">
-        <v>24</v>
-      </c>
-      <c r="E56" t="n">
-        <v>24</v>
-      </c>
-      <c r="F56" t="n">
-        <v>42</v>
-      </c>
-      <c r="G56" t="n">
-        <v>23</v>
+        <v>38</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>S Comp +15</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>202</v>
-      </c>
-      <c r="C57" t="n">
-        <v>46</v>
-      </c>
-      <c r="D57" t="n">
-        <v>25</v>
-      </c>
-      <c r="E57" t="n">
-        <v>26</v>
-      </c>
-      <c r="F57" t="n">
-        <v>30</v>
+          <t>P Comp -15</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Ter -15</t>
+          <t>P Comp +15</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>557</v>
+        <v>225</v>
       </c>
       <c r="C58" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="D58" t="n">
+        <v>30</v>
+      </c>
+      <c r="E58" t="n">
+        <v>35</v>
+      </c>
+      <c r="F58" t="n">
+        <v>40</v>
+      </c>
+      <c r="G58" t="n">
         <v>29</v>
-      </c>
-      <c r="E58" t="n">
-        <v>43</v>
-      </c>
-      <c r="F58" t="n">
-        <v>48</v>
-      </c>
-      <c r="G58" t="n">
-        <v>32</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Ter +15</t>
+          <t>S Inc -15</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>541</v>
-      </c>
-      <c r="C59" t="n">
-        <v>65</v>
-      </c>
-      <c r="D59" t="n">
+        <v>111</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G59" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>S Inc+15</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>199</v>
+      </c>
+      <c r="C60" t="n">
+        <v>34</v>
+      </c>
+      <c r="D60" t="n">
+        <v>30</v>
+      </c>
+      <c r="E60" t="n">
+        <v>23</v>
+      </c>
+      <c r="F60" t="n">
+        <v>33</v>
+      </c>
+      <c r="G60" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>S Comp -15</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>272</v>
+      </c>
+      <c r="C61" t="n">
         <v>36</v>
       </c>
-      <c r="E59" t="n">
-        <v>57</v>
-      </c>
-      <c r="F59" t="n">
-        <v>48</v>
-      </c>
-      <c r="G59" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>2023</v>
+      <c r="D61" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="E61" t="n">
+        <v>37</v>
+      </c>
+      <c r="F61" t="n">
+        <v>36</v>
+      </c>
+      <c r="G61" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>habilidad</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>Central</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>Chorotega</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>Pacífico Central</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>Brunca</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>Huetar Caribe</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>Huetar Norte</t>
-        </is>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>S Comp +15</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>209</v>
+      </c>
+      <c r="C62" t="n">
+        <v>29</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F62" t="n">
+        <v>30</v>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>P Comp +15</t>
+          <t>Ter -15</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>197</v>
+        <v>624</v>
       </c>
       <c r="C63" t="n">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="D63" t="n">
-        <v>28</v>
-      </c>
-      <c r="E63" s="3" t="n">
-        <v>17</v>
+        <v>38</v>
+      </c>
+      <c r="E63" t="n">
+        <v>59</v>
       </c>
       <c r="F63" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G63" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S Inc -15</t>
+          <t>Ter +15</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>70</v>
-      </c>
-      <c r="C64" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="D64" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="E64" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F64" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="G64" s="3" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>S Inc+15</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>167</v>
-      </c>
-      <c r="C65" t="n">
-        <v>23</v>
-      </c>
-      <c r="D65" t="n">
-        <v>22</v>
-      </c>
-      <c r="E65" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="F65" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="G65" s="3" t="n">
-        <v>16</v>
+        <v>518</v>
+      </c>
+      <c r="C64" t="n">
+        <v>57</v>
+      </c>
+      <c r="D64" t="n">
+        <v>27</v>
+      </c>
+      <c r="E64" t="n">
+        <v>49</v>
+      </c>
+      <c r="F64" t="n">
+        <v>34</v>
+      </c>
+      <c r="G64" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>S Comp -15</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>311</v>
-      </c>
-      <c r="C66" t="n">
-        <v>29</v>
-      </c>
-      <c r="D66" t="n">
-        <v>26</v>
-      </c>
-      <c r="E66" t="n">
-        <v>31</v>
-      </c>
-      <c r="F66" t="n">
-        <v>55</v>
-      </c>
-      <c r="G66" t="n">
-        <v>24</v>
+      <c r="A66" t="n">
+        <v>2022</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>S Comp +15</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
-        <v>223</v>
-      </c>
-      <c r="C67" t="n">
-        <v>39</v>
-      </c>
-      <c r="D67" t="n">
-        <v>27</v>
-      </c>
-      <c r="E67" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="F67" t="n">
-        <v>25</v>
-      </c>
-      <c r="G67" s="3" t="n">
-        <v>14</v>
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>habilidad</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Chorotega</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Pacífico Central</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Brunca</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Huetar Caribe</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Huetar Norte</t>
+        </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Ter -15</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>515</v>
-      </c>
-      <c r="C68" t="n">
-        <v>53</v>
-      </c>
-      <c r="D68" t="n">
-        <v>29</v>
-      </c>
-      <c r="E68" t="n">
-        <v>41</v>
-      </c>
-      <c r="F68" t="n">
-        <v>48</v>
-      </c>
-      <c r="G68" t="n">
-        <v>36</v>
+          <t>P Inc -15</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>P Inc +15</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>23</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>P Comp -15</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G70" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>P Comp +15</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>156</v>
+      </c>
+      <c r="C71" t="n">
+        <v>24</v>
+      </c>
+      <c r="D71" t="n">
+        <v>22</v>
+      </c>
+      <c r="E71" t="n">
+        <v>23</v>
+      </c>
+      <c r="F71" t="n">
+        <v>27</v>
+      </c>
+      <c r="G71" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>S Inc -15</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>63</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G72" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>S Inc+15</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>170</v>
+      </c>
+      <c r="C73" t="n">
+        <v>27</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>S Comp -15</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>277</v>
+      </c>
+      <c r="C74" t="n">
+        <v>37</v>
+      </c>
+      <c r="D74" t="n">
+        <v>24</v>
+      </c>
+      <c r="E74" t="n">
+        <v>24</v>
+      </c>
+      <c r="F74" t="n">
+        <v>42</v>
+      </c>
+      <c r="G74" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>S Comp +15</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>202</v>
+      </c>
+      <c r="C75" t="n">
+        <v>46</v>
+      </c>
+      <c r="D75" t="n">
+        <v>25</v>
+      </c>
+      <c r="E75" t="n">
+        <v>26</v>
+      </c>
+      <c r="F75" t="n">
+        <v>30</v>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Ter -15</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>557</v>
+      </c>
+      <c r="C76" t="n">
+        <v>55</v>
+      </c>
+      <c r="D76" t="n">
+        <v>29</v>
+      </c>
+      <c r="E76" t="n">
+        <v>43</v>
+      </c>
+      <c r="F76" t="n">
+        <v>48</v>
+      </c>
+      <c r="G76" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
           <t>Ter +15</t>
         </is>
       </c>
-      <c r="B69" t="n">
+      <c r="B77" t="n">
+        <v>541</v>
+      </c>
+      <c r="C77" t="n">
+        <v>65</v>
+      </c>
+      <c r="D77" t="n">
+        <v>36</v>
+      </c>
+      <c r="E77" t="n">
+        <v>57</v>
+      </c>
+      <c r="F77" t="n">
+        <v>48</v>
+      </c>
+      <c r="G77" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>habilidad</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Chorotega</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Pacífico Central</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Brunca</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>Huetar Caribe</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Huetar Norte</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>P Inc -15</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>P Inc +15</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>30</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>P Comp -15</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>21</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>P Comp +15</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>176</v>
+      </c>
+      <c r="C84" t="n">
+        <v>21</v>
+      </c>
+      <c r="D84" t="n">
+        <v>26</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F84" t="n">
+        <v>26</v>
+      </c>
+      <c r="G84" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>S Inc -15</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>70</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>S Inc+15</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>167</v>
+      </c>
+      <c r="C86" t="n">
+        <v>23</v>
+      </c>
+      <c r="D86" t="n">
+        <v>22</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>S Comp -15</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>311</v>
+      </c>
+      <c r="C87" t="n">
+        <v>29</v>
+      </c>
+      <c r="D87" t="n">
+        <v>26</v>
+      </c>
+      <c r="E87" t="n">
+        <v>31</v>
+      </c>
+      <c r="F87" t="n">
+        <v>55</v>
+      </c>
+      <c r="G87" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>S Comp +15</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>223</v>
+      </c>
+      <c r="C88" t="n">
+        <v>39</v>
+      </c>
+      <c r="D88" t="n">
+        <v>27</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F88" t="n">
+        <v>25</v>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Ter -15</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>515</v>
+      </c>
+      <c r="C89" t="n">
+        <v>53</v>
+      </c>
+      <c r="D89" t="n">
+        <v>29</v>
+      </c>
+      <c r="E89" t="n">
+        <v>41</v>
+      </c>
+      <c r="F89" t="n">
+        <v>48</v>
+      </c>
+      <c r="G89" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Ter +15</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
         <v>561</v>
       </c>
-      <c r="C69" t="n">
+      <c r="C90" t="n">
         <v>61</v>
       </c>
-      <c r="D69" t="n">
+      <c r="D90" t="n">
         <v>33</v>
       </c>
-      <c r="E69" t="n">
+      <c r="E90" t="n">
         <v>52</v>
       </c>
-      <c r="F69" t="n">
+      <c r="F90" t="n">
         <v>49</v>
       </c>
-      <c r="G69" t="n">
+      <c r="G90" t="n">
         <v>35</v>
       </c>
     </row>
